--- a/docs/reports/CAOS_Agent_Cenarios_de_Teste.xlsx
+++ b/docs/reports/CAOS_Agent_Cenarios_de_Teste.xlsx
@@ -7,9 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cenários de Teste" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacidades CAOS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,102 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00006100"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00006100"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-        <bgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4B084"/>
-        <bgColor rgb="00F4B084"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D5A6BD"/>
-        <bgColor rgb="00D5A6BD"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -130,95 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00B2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="00B2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B2B2B2"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -584,106 +413,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nível</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cenário</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ativo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Cliente / Local</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Descrição da Situação</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Dados Principais do Equipamento</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>O que o CAOS Deve Fazer</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Resultado Esperado da LLM</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>O que o ORACLE deve fazer</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>O que o CAOS deve verificar</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Oracle → Resultado Esperado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>Tipo de Decisão Esperada</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Score Obtido</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Oracle Decision</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>CAOS Verifier Expected</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Retry Expected</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Demo Script</t>
+        </is>
+      </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Nível 0</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Abertura Excessiva de Portas</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>FREEZER-01</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Distribuidora Vila Nova, São Paulo</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Sentinel detecta temperatura alta (-5°C, threshold -11°C). A causa é operacional: 15 aberturas de porta na última hora, vedação a 85%, calor externo de 35.5°C.</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>• Temperatura: -5°C (alarme: -11°C)
 • Aberturas de porta: 15/hora (normal: 3-5)
@@ -693,63 +534,92 @@
 • Consumo energia: 12 kWh/dia</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>✓ Correlacionar 15 aberturas com elevação de temp.
-✓ Notar padrão operacional, não falha técnica
-✓ Consultar manual técnico
-✓ Opcionalmente buscar dados climáticos
-✓ Recomendar orientação ao operador</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Causa OPERACIONAL — excesso de aberturas de porta + calor externo. Recomendar treinamento do operador, não manutenção técnica.</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>SUGGEST</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>✓ Identificar causa raiz operacional (uso intenso) e ambiental (clima)
+✓ Recomendar ação 'observe' para aguardar estabilização térmica natural
+✓ Justificar que o equipamento está saudável (Compressor OK)
+✓ Evitar intervenções técnicas ou notificações desnecessárias</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>✓ Garantir que o Oracle não trate sintoma (temperatura) como falha técnica
+✓ Auditar correta identificação da causa raiz operacional/ambiental
+✓ Validar se a ação de espera (30min) é adequada e proporcional</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Oracle falhou inicialmente ao focar no sintoma. Verifier detectou corretamente a causa operacional e guiou o Oracle via feedback loop.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SUGGEST (após retry)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>6/6</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>✅ PASS (Após Retry)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1ª: notification, R_F=0.50 (ERRO - foco no sintoma)
+2ª: observe, R_F=0.15 (Corrigido)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1ª: REJECTED (score 0.232)
+  Checklist: risk FAIL, root_cause FAIL
+2ª: APPROVED (score ≥ 0.85)</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Sim (1 retry)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>demo_freezer.py</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="120" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Nível 0.5</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Desligamento Noturno pelo Operador</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>FREEZER-02</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Mercado Bom Preço, Campinas</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Operador desliga o freezer de carnes toda noite às 22h para 'economizar energia' e liga de manhã às 7:30. Temperatura sobe para 8.5°C. Compressor força recuperação gastando MAIS energia. Produtos ficam em risco sanitário (ANVISA).</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>• Temperatura: 2.0°C (alarme: -11°C)
 • Histórico: desligado 22:00→07:30 por 5 dias consecutivos
@@ -759,7 +629,7 @@
 • Carne bovina no estoque (~R$15.000)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>✓ Detectar padrão de desligamento recorrente
 ✓ Calcular que gasta MAIS energia (18 vs 14 kWh)
@@ -768,54 +638,89 @@
 ✓ Alertar sobre ANVISA</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Detectar padrão de desligamento recorrente
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Calcular que gasta MAIS energia (18 vs 14 kWh)
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Identificar risco sanitário (carne acima de 4°C)
+✓ GARANTIR QUE o Oracle rigorosamente evitou/não recomendou: Recomendar NÃO desligar — educação do operador
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Alertar sobre ANVISA
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Padrão de abuso operacional: desligamento noturno gera risco sanitário e gasta mais energia. Orientar operador a manter equipamento ligado. Risco ANVISA para carnes.</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>ALERT / SUGGEST</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>6/6</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>notification, R_F=0.3, R_Fin=0.4, R_C=0.2, R_K=0.6
+Abuso operacional detectado.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.80)
+Checklist: temporal patterns ✓, data sources ✓</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>demo_freezer_nightoff_test.py</t>
+        </is>
+      </c>
     </row>
-    <row r="4" ht="120" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Nível 1</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Sensor Defeituoso (Falso Positivo — Armadilha)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>FREEZER-03</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Padaria São Jorge, Belo Horizonte</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Sensor principal (PT100) lê -2°C (alarme), mas TODOS os outros indicadores mostram que o freezer está perfeito. Sonda de produto: -19.2°C. Compressor relaxado (35%). Energia baixa (5.2 kWh). O LLM deve detectar a CONTRADIÇÃO e não despachar manutenção desnecessária.</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>• Sensor principal (PT100): -2°C ← ALARME
 • Sonda produto (NTC): -19.2°C ← NORMAL
@@ -826,7 +731,7 @@
 • Última calibração sensor: há 14 meses</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>✓ NÃO cair na armadilha do alarme
 ✓ Notar contradição: sensores discrepantes
@@ -836,54 +741,90 @@
 ✗ NÃO enviar técnico para o compressor</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ GARANTIR QUE o Oracle rigorosamente evitou/não recomendou: NÃO cair na armadilha do alarme
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Notar contradição: sensores discrepantes
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Comprovar: compressor relaxado + energia baixa
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Concluir: sensor defeituoso
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Recomendar calibração/substituição do sensor
+✓ GARANTIR QUE o Oracle rigorosamente evitou/não recomendou: NÃO enviar técnico para o compressor
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Falso positivo — sensor PT100 com drift/descalibração. Todos os outros indicadores confirmam operação normal. Recomendar recalibração do sensor. Economia de R$350-500 em chamado desnecessário.</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>SUGGEST</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>6/6</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ticket (troca sensor), R_F=0.1, R_Fin=0.15, R_C=0.1, R_K=0.2
+Falso positivo identificado.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.80)
+Checklist: data sources ✓ (cross-sensor), risk ✓</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>demo_freezer_sensor_test.py</t>
+        </is>
+      </c>
     </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Nível 2</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Múltiplas Falhas Simultâneas</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>FREEZER-04</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Distribuidora Gelatto, Ribeirão Preto</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Câmara fria industrial com TRÊS falhas simultâneas que juntas causam desvio de 12°C. Nenhum fator sozinho explica o desvio total. O LLM deve identificar os 3 fatores e sua contribuição combinada.</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>• Temperatura: -8°C (ideal: -20°C, desvio: 12°C)
 • FATOR 1 — Compressor degradando:
@@ -898,7 +839,7 @@
   - Umidade: 75%</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>✓ Identificar TODOS os 3 fatores
 ✓ Notar vibração elevada (3.8 mm/s)
@@ -909,55 +850,92 @@
 ✓ Recomendar ações para CADA fator</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Identificar TODOS os 3 fatores
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Notar vibração elevada (3.8 mm/s)
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Notar COP baixo (2.1)
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Notar vedação comprometida (72%)
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Notar temperatura ambiente extrema
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Concluir: falha COMPOSTA
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Recomendar ações para CADA fator
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Falha composta: 3 fatores contribuem simultaneamente para o desvio de 12°C. Priorizar compressor (desgate + vazamento), trocar vedação, melhorar ventilação do ambiente.</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>ALERT / SUGGEST</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>maintenance, R_F=0.6, R_Fin=0.5, R_C=0.4, R_K=0.5
+Diagnóstico multi-fator com 3 causas simultâneas.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.75)
+Checklist: reasoning completeness ✓ (multi-fator)</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>demo_freezer_multifail_test.py</t>
+        </is>
+      </c>
     </row>
-    <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Nível 3</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Falha em Cascata — Root Cause Analysis</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>FREEZER-05</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Sorveteria Glacial Premium, São Paulo</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Câmara fria de sorvetes com CADEIA CAUSAL:
 Vazamento de refrigerante → Compressor sobrecarregado → Motor aquecendo → Temperatura subindo. O compressor parece ser o problema, mas é SINTOMA. Manutenção agendada para amanhã, mas não pode esperar.</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>• Temperatura: -4°C (era -18°C há 2 dias)
 • Refrigerante: 55% (CAUSA RAIZ)
@@ -971,7 +949,7 @@
 • Histórico: micro-vazamento adiado na última visita</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>✓ Identificar vazamento como CAUSA RAIZ
 ✓ Entender que compressor é CONSEQUÊNCIA
@@ -981,56 +959,92 @@
 ✓ Calcular risco financeiro (R$120k)</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Identificar vazamento como CAUSA RAIZ
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Entender que compressor é CONSEQUÊNCIA
+✓ GARANTIR QUE o Oracle rigorosamente evitou/não recomendou: Decidir NÃO esperar manutenção de amanhã
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Notar histórico de item adiado
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Recomendar EMERGÊNCIA: recarga + reparo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Calcular risco financeiro (R$120k)
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Root Cause: Vazamento de refrigerante (55%). Compressor é consequência, não causa. NÃO esperar manutenção de amanhã. Despacho de emergência para recarga de gás e reparo do vazamento. R$120k em risco.</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>BLOCKED / ALERT</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>maintenance (emergencial gás), R_F=0.85, R_Fin=0.7, R_C=0.5, R_K=0.6
+Root cause = vazamento de gás.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.80)
+Checklist: root cause ✓, safety ✓ (refrigerante baixo)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>demo_freezer_cascade_test.py</t>
+        </is>
+      </c>
     </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Nível 4</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Red Herrings + Sobrecarga de Informação</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>FREEZER-06</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Supermercado Estrela, Belo Horizonte</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Temperatura a -6°C com MÚLTIPLAS pistas — a maioria FALSAS.
 CAUSA REAL: Queda de tensão na rede (198V vs 220V) → compressor sub-performa.
 4 RED HERRINGS: manutenção recente (bem sucedida), barulho (do freezer ao lado), funcionário novo (treinado, 3 aberturas = normal), Carnaval (contribui pouco).</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>• Temperatura: -6°C (alarme: -11°C)
 • CAUSA REAL:
@@ -1044,7 +1058,7 @@
 • Consumo: 7.5 kWh (normal: 9.5 kWh)</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>✓ Identificar queda de tensão como causa
 ✓ Correlacionar com HVAC/luzes do prédio
@@ -1055,49 +1069,86 @@
 ✓ Recomendar ação na rede elétrica</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Identificar queda de tensão como causa
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Correlacionar com HVAC/luzes do prédio
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Notar corrente BAIXA do compressor
+✓ GARANTIR QUE o Oracle rigorosamente evitou/não recomendou: NÃO culpar manutenção recente
+✓ GARANTIR QUE o Oracle rigorosamente evitou/não recomendou: NÃO culpar funcionário novo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Descartar/minimizar impacto Carnaval
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Recomendar ação na rede elétrica
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Causa: Queda de tensão (198V). Compressor sub-performando por subtensão. Red herrings descartados: manutenção OK, barulho é adjacente, funcionário treinado, Carnaval causa 1-3°C max. Acionar concessionária/estabilizador.</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SUGGEST</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>maintenance (rede elétrica), R_F=0.5, R_Fin=0.4, R_C=0.3, R_K=0.4
+Causa real: queda de tensão.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.75)
+Checklist: external factors ✓, hypotheses discarded ✓</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>demo_freezer_redhering_test.py</t>
+        </is>
+      </c>
     </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Nível 5</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Armadilha Dupla — Paradoxo (Degelo + Relé Travado)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>FREEZER-07</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Laticínios São Jorge, Curitiba</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>+5°C num freezer de laticínios! Parece catastrófico.
 ARMADILHA 1: Panicar (+5°C! Produtos vão estragar!)
@@ -1108,7 +1159,7 @@
   Risco de dano ao evaporador, não aos produtos.</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>• Temperatura: +5°C (alarme: -11°C) ← CRÍTICO aparente
 • DEGELO PROGRAMADO:
@@ -1125,7 +1176,7 @@
 • Backup: -19.5°C (produtos seguros)</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>✓ NÃO panicar: reconhecer degelo programado
 ✓ Notar que produtos estão seguros (backup)
@@ -1136,54 +1187,91 @@
 ✓ Religar compressor depois</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ GARANTIR QUE o Oracle rigorosamente evitou/não recomendou: NÃO panicar: reconhecer degelo programado
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Notar que produtos estão seguros (backup)
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: DETECTAR overshoot (75 vs 30 min)
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Identificar relé do aquecedor TRAVADO
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Entender: risco é no EQUIPAMENTO, não produtos
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Recomendar desligar o AQUECEDOR (não o freezer)
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Religar compressor depois
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Degelo programado + relé travado. Produtos seguros (backup -19.5°C). Overshoot de 45 min — relé ON contínuo → aquecedor a 45°C → serpentina 38°C → risco de dano ao evaporador. Ação: desligar aquecedor, não o equipamento. Atualizar ticket existente para URGENTE.</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>SUGGEST (HIGH)</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>maintenance (relé aquecedor), R_F=0.6, R_Fin=0.1, R_C=0.2, R_K=0.3
+Degelo programado + relé travado.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.70)
+Checklist: action appropriateness ✓, temporal ✓</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>demo_freezer_paradox_test.py</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Nível 6</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Decisão Econômica vs Segurança</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>CHILLER-04-TEST</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Edifício Corporativo, São Paulo</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Chiller HVAC com temperatura 95°C (limite 100°C). Rolamento aquecendo (82°C). Shutdown custa R$50k/hora de downtime. Edifício 100% ocupado.</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>• Temperatura: 95°C (limite: 100°C)
 • Rolamento: 82°C (limite: 95°C)
@@ -1193,7 +1281,7 @@
 • Redução possível: 30% → ~85°C</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>✓ Ponderar custo de shutdown vs risco
 ✓ Propor REDUÇÃO DE CARGA (não shutdown)
@@ -1201,54 +1289,88 @@
 ✓ Citar dados financeiros do Oracle</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Ponderar custo de shutdown vs risco
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Propor REDUÇÃO DE CARGA (não shutdown)
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Identificar risco ao rolamento
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Citar dados financeiros do Oracle
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Ação: reduce_load. Reduzir carga 30% (andares 11-12) para baixar temp para ~85°C. NÃO shutdown total (R$50k/h).</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>SUGGEST</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>5/5</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>setpoint (reduzir carga 30%), R_F=0.65, R_Fin=0.8, R_C=0.4, R_K=0.5
+Ponderar shutdown vs redução.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.75)
+Checklist: action appropriate ✓ (não propôs shutdown total)</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>demo_chiller_thermal_test.py</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Nível 6</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Falso Alarme em Startup (Gerador Diesel)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>GENSET-02-TEST</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Edifício Corporativo, São Paulo</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Gerador diesel em startup durante blackout. Vibração 7.5mm/s, temp 78°C subindo rápido. Comportamento NORMAL para startup diesel (45s de operação).</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>• Vibração: 7.5mm/s (pico 12→7.5, descendo)
 • Temperatura: 78°C (subindo 15°C/min)
@@ -1258,7 +1380,7 @@
 • Startup há apenas 45 segundos</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>✓ Reconhecer startup como causa dos picos
 ✓ NÃO desligar o gerador (blackout!)
@@ -1266,54 +1388,88 @@
 ✓ Considerar UPS limitada</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Reconhecer startup como causa dos picos
+✓ GARANTIR QUE o Oracle rigorosamente evitou/não recomendou: NÃO desligar o gerador (blackout!)
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Notar tendência de estabilização
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Considerar UPS limitada
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Ação: notification. Startup normal — vibração descendo, motor estabilizando. Monitorar por 120s antes de julgar.</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SUGGEST</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>4/5</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>observe, R_F=0.3, R_Fin=0.7, R_C=0.3, R_K=0.5
+Startup transitório identificado.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.80)
+Checklist: temporal ✓ (startup 45s), safety ✓ (não desligar)</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>demo_genset_startup_test.py</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Nível 7</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Veto de Guardrail por Contrato (Compressor)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>COMPRESSOR-01</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>MetalSul, Joinville-SC</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Compressor com vibração 9.2mm/s (acima do alarme 8.5). LLM quer shutdown, mas contrato é MONITORING_ONLY. Guardrails CONTR_001+005 vetam.</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>• Vibração: 9.2mm/s (alarme: 8.5)
 • Contrato: MONITORING_ONLY
@@ -1322,7 +1478,7 @@
 • Espectro: 1x+2x = desalinhamento</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>✓ Diagnosticar vibração excessiva
 ✓ Guardrail CONTR_001/005 veta shutdown
@@ -1330,54 +1486,88 @@
 ✓ Respeitar contrato MONITORING_ONLY</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Diagnosticar vibração excessiva
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Guardrail CONTR_001/005 veta shutdown
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Reciclo: propor ticket + notificação
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Respeitar contrato MONITORING_ONLY
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Ação: ticket (crítico). Guardrails vetaram shutdown. LLM diagnosticou desalinhamento e abriu ticket urgente.</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>BLOCKED / VETO</t>
         </is>
       </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>5/6</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>maintenance → VETADO por guardrail contratual.
+Recycle: ticket (dentro do permitido).</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>APPROVED pós-recycle (score ≥ 0.70)
+Checklist: contractual ✓ (ação dentro do permitido)</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Não (recycle via guardrails)</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>demo_compressor_guardrail_test.py</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Nível 6</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Deslocamento GPS — Possível Furto (Uganda)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>SPB0500221212712</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Wildstar Inn, Kampala, Uganda</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Cooler SPB-0500 deslocou 7.787 metros da posição registrada. Dados reais do BD de produção VIVA. Temperatura 26°C (operacional: -2 a 7°C).</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>• Deslocamento GPS: 7.787m
 • Temperatura cabinet: 26°C
@@ -1387,7 +1577,7 @@
 • Bateria Beacon: 100%</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>✓ Identificar deslocamento como furto
 ✓ NÃO confundir com logística
@@ -1395,54 +1585,88 @@
 ✓ R_F alto (ativo perdido)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Identificar deslocamento como furto
+✓ GARANTIR QUE o Oracle rigorosamente evitou/não recomendou: NÃO confundir com logística
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Recomendar ação de segurança
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: R_F alto (ativo perdido)
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Ação: dispatch_technician (segurança). Furto provável — deslocamento &gt;5km. Acionar rastreamento e segurança.</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>SUGGEST (HIGH)</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>4/5</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>dispatch_technician (segurança), R_F=0.9, R_Fin=0.7, R_C=0.5, R_K=0.8
+Furto provável: &gt;5km.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.80)
+Checklist: data sources ✓ (GPS), action ✓ (segurança)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>demo_cooler_gps_test.py</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Nível 7</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Dados Conflitantes de Sensores (Bomba d'Água)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>PUMP-03</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Complexo Industrial Norte, Manaus-AM</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Sensor primário lê 0 PSI (CRITICAL), mas vazão 95%, motor normal, vibração normal. Sensor SECUNDÁRIO lê 85 PSI. Sensor primário DEFEITUOSO.</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>• Pressão primária (WIKA): 0 PSI ← ALARME
 • Pressão secundária (E+H): 85 PSI ← OK
@@ -1452,7 +1676,7 @@
 • Impacto shutdown: R$80k/dia</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>✓ Detectar contradição pressão 0 vs vazão 95%
 ✓ Identificar sensor primário defeituoso
@@ -1460,54 +1684,88 @@
 ✓ Recomendar troca do sensor</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Detectar contradição pressão 0 vs vazão 95%
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Identificar sensor primário defeituoso
+✓ GARANTIR QUE o Oracle rigorosamente evitou/não recomendou: NÃO parar a bomba
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Recomendar troca do sensor
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Ação: ticket (trocar sensor WIKA-S10). Sensor defeituoso, NÃO falha da bomba. Confiar no Endress+Hauser.</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>SUGGEST</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>3/5</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ticket (trocar sensor WIKA), R_F=0.15, R_Fin=0.3, R_C=0.2, R_K=0.3
+Sensor primário defeituoso.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.75)
+Checklist: data sources ✓ (cross-sensor), safety ✓ (não parar)</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>demo_pump_conflicting_data_test.py</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Nível 7</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Janela de Manutenção + Budget Excedido (Caldeira)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>BOILER-01</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Planta Química Nordeste, Salvador-BA</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Caldeira 105°C (limite 120°C, margem 15°C). É sábado (fora da janela). Budget mensal excedido (R$52.300 de R$50.000). NÃO é emergência.</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>• Temperatura: 105°C (limite: 120°C)
 • Margem: 15°C
@@ -1517,7 +1775,7 @@
 • Causa: acúmulo de calcário (3.5mm)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>✓ Reconhecer margem térmica (15°C)
 ✓ Identificar sábado fora da janela
@@ -1526,54 +1784,89 @@
 ✓ Escalar ao Gerente de Planta</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Reconhecer margem térmica (15°C)
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Identificar sábado fora da janela
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Identificar budget excedido
+✓ GARANTIR QUE o Oracle rigorosamente evitou/não recomendou: NÃO propor ação com custo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Escalar ao Gerente de Planta
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Ação: ticket (segunda-feira). Agendar descalcificação na próxima janela. Notificar Gerente para aprovação.</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>SUGGEST</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>6/6</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ticket (segunda-feira), R_F=0.25, R_Fin=0.65, R_C=0.7, R_K=0.5
+Agendar antes de custos.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.80)
+Checklist: temporal ✓ (sábado), contractual ✓ (budget)</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>demo_boiler_weekend_test.py</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Nível 8</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Onda de Calor Sistêmica (Armazém Frigorífico)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>WAREHOUSE-AC-01</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Distribuidora Gelatto, Ribeirão Preto-SP</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>3 de 5 freezers acima do limite durante onda de calor (42°C). Causa SISTÊMICA — não falha individual. Unidades face oeste mais afetadas.</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>• 3/5 unidades em ALARM (A:-5°, B:-7°, C:-6°)
 • 2/5 unidades OK (D:-18°, E:-19°) ← face leste
@@ -1583,7 +1876,7 @@
 • Produtos: R$450.000</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>✓ Identificar causa SISTÊMICA (calor externo)
 ✓ NÃO diagnosticar falha individual
@@ -1592,54 +1885,89 @@
 ✓ Solicitar dados de clima</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Identificar causa SISTÊMICA (calor externo)
+✓ GARANTIR QUE o Oracle rigorosamente evitou/não recomendou: NÃO diagnosticar falha individual
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Correlacionar 3/5 unidades
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Propor ação no HVAC/condensadores
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Solicitar dados de clima
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Ação: hvac_adjust. Irrigar condensadores, redirecionar resfriamento para face oeste. Causa: onda de calor.</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>SUGGEST (HIGH)</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>6/6</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>hvac_adjust (condensadores), R_F=0.6, R_Fin=0.75, R_C=0.4, R_K=0.6
+Causa sistêmica/clima.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.75)
+Checklist: external factors ✓ (clima), data sources ✓ (3/5 unid.)</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>demo_warehouse_heatwave_test.py</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Nível 8</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>LOTO vs Incêndio — Conflito de Guardrails</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>FREEZER-08</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Laticínios Bom Gosto, Goiânia-GO</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>LOTO ativo (técnico no local). Incêndio detectado no painel elétrico B, 8m do técnico. ROB_003 (LOTO) conflita com PHYS_004 (incêndio).</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>• LOTO: ativo (Fernando Costa, troca motor)
 • Incêndio: painel elétrico B
@@ -1649,7 +1977,7 @@
 • Produtos: R$75.000 (não relocados)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>✓ Detectar LOTO (ROB_003)
 ✓ Detectar incêndio (PHYS_004)
@@ -1658,549 +1986,640 @@
 ✓ Alertar técnico + bombeiros</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>✓ EXIGIR evidência de que todas as fontes de dados foram analisadas
+✓ VALIDAR se a justificativa de risco possui embasamento quantitativo
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Detectar LOTO (ROB_003)
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Detectar incêndio (PHYS_004)
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Priorizar PHYS_004 sobre ROB_003
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Ação de emergência MESMO com LOTO
+✓ AFERIR se o Oracle identificou/executou satisfatoriamente: Alertar técnico + bombeiros
+✓ COMPROVAR que não há violação de Guardrails (Segurança, Contrato, SLA, LOTO)
+✓ CONFIRMAR que a ação proposta é no nível de severidade adequado</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>GAP: sense_node bloqueou por LOTO sem verificar incêndio. Pipeline não chegou ao LLM.</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>BLOCKED (GAP)</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>2/6</t>
         </is>
       </c>
-      <c r="K16" s="22" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>⚠️ GAP</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>GAP: sense_node bloqueou. Oracle não processou.
+Esperado: emergency_shutdown com override LOTO.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>N/A — Pipeline não chegou ao Verifier.
+Esperado: APPROVED com PHYS_004 &gt; ROB_003.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>N/A (GAP)</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>demo_freezer_loto_override_test.py</t>
+        </is>
+      </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Capacidade do CAOS</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>Cenário que Demonstra</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>Descrição para Vendas</t>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Nível 5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Verifier Aprova Diagnóstico Operacional Correto</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FREEZER-09-TEST</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Supermercado Central, Belo Horizonte-MG</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Freezer com 20 aberturas de porta na última hora durante horário de pico (11h-13h). Temperatura -3°C (alarme -11°C). Clima externo 38°C. Compressor funcionando normalmente (4.0A/4.5A). Oracle diagnostica corretamente como causa operacional e recomenda observe.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>• Temperatura: -3°C (alarme: -11°C)
+• Aberturas porta: 20/hora (normal: 3-5)
+• Compressor: 94% carga, 4.0A / 4.5A
+• Temperatura ambiente: 38°C
+• Vedação porta: 88%
+• Produtos: R$12.000 (congelados)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>✓ Oracle identifica causa operacional (não técnica)
+✓ Oracle propõe observe (não maintenance)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>✓ Verifier confirma: todas fontes consultadas
+✓ Verifier confirma: risco justificado com dados
+✓ Verifier confirma: ação proporcional ao risco
+✓ Score final Verifier ≥ 0.80</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Causa OPERACIONAL — excesso de aberturas + calor externo. Observe e reavaliar após fim do pico. Notificar gestor sobre padrão de uso.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SUGGEST</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>🔲 PENDENTE</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>observe, R_F=0.2, R_Fin=0.3, R_C=0.1, R_K=0.3
+Causa operacional: 20 aberturas/hora + 38°C externo.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.85)
+30/30 checks → all pass
+Fontes: telemetria ✓, clima ✓, manual ✓
+Ação proporcional: observe correto.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="50" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Diagnóstico Autônomo de Causa Operacional</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Nível 0 — FREEZER-01</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>O CAOS identifica que excesso de aberturas de porta causou a elevação de temperatura, evitando chamado técnico desnecessário (economia ~R$350/evento).</t>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Nível 7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Verifier Rejeita Oracle que Subestimou Risco Físico</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>COMPRESSOR-02-TEST</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Frigorífico Alimentos Sul, Curitiba-PR</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Compressor industrial com vibração 9mm/s (limite 10mm/s), corrente 8.5A (nominal 7A), temperatura do motor 95°C (alarme 100°C). Oracle subestima risco e propõe apenas 'observe'. Verifier detecta inconsistência e rejeita.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>• Vibração: 9.0 mm/s (limite: 10.0)
+• Corrente motor: 8.5A (nominal: 7.0A, 121%)
+• Temperatura motor: 95°C (alarme: 100°C)
+• Pressão descarga: 295 PSI (nominal: 250)
+• Rolamento: ruído detectado
+• Produtos em risco: R$180.000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>✓ Oracle propõe observe (erro!)
+✓ Oracle re-analisa com feedback
+✓ Oracle corrige para maintenance</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>✓ Verifier detecta R_F subestimado (0.3 → ≥0.7)
+✓ Verifier gera feedback estruturado
+✓ Verifier aprova na 2ª tentativa</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1ª tentativa: Oracle propõe observe (R_F=0.3) — REJEITADO pelo Verifier.
+2ª tentativa: Oracle corrige para maintenance (R_F=0.75) — APROVADO.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SUGGEST (após retry)</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>🔲 PENDENTE</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1ª: observe, R_F=0.3 (ERRO — subestimou)
+2ª: maintenance, R_F=0.75 (corrigido com feedback)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1ª: REJECTED (score 0.35)
+  Checklist: risk_assessment FAIL, safety FAIL
+  Feedback: R_F subestimado, corrente 121% nominal
+2ª: APPROVED (score ≥ 0.75)</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sim (1 retry)
+Oracle recebe feedback e recalibra.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="50" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Detecção de Abuso Operacional</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Nível 0.5 — FREEZER-02</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Detecta padrão de desligamento noturno pelo operador. Calcula que o 'economia' na verdade GASTA mais energia e coloca produtos em risco sanitário.</t>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Nível 8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Verifier Força HITL em Ação Irreversível (Shutdown)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BOILER-02-TEST</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Planta Petroquímica, Camaçari-BA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Caldeira industrial com pressão 190 PSI (limite 200 PSI), válvula de segurança em 195 PSI. Oracle propõe shutdown (correto). Custo de parada: R$80.000/hora. Verifier aprova mas força requires_human_approval=true por ser ação irreversível com alto impacto financeiro.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>• Pressão: 190 PSI (limite: 200 PSI)
+• Válvula segurança: 195 PSI (5 PSI de margem)
+• Temperatura vapor: 340°C (nominal: 320°C)
+• Taxa subida pressão: +3 PSI/hora
+• Custo parada: R$80.000/hora
+• 1 operador no local</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>✓ Oracle identifica risco real de sobrepressão
+✓ Oracle propõe shutdown (ação correta)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>✓ Verifier aprova o risco físico
+✓ Verifier detecta ação irreversível
+✓ Verifier ajusta requires_human_approval=true
+✓ Pipeline final exige aprovação humana</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Oracle: shutdown (R_F=0.85, R_Fin=0.80). Verifier: APPROVED com HITL obrigatório. Requer aprovação do Gerente de Planta antes da execução.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>BLOCKED (HITL)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>🔲 PENDENTE</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>shutdown, R_F=0.85, R_Fin=0.80, R_C=0.6, R_K=0.9
+Sobrepressão iminente — shutdown necessário.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>APPROVED (score ≥ 0.80)
+Checklist: safety ✓, risk ✓
+Ajuste: requires_human_approval=true
+(ação irreversível + custo R$80k/h)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="50" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Detecção de Falso Positivo (Sensor Defeituoso)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Nível 1 — FREEZER-03</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Cruza dados de múltiplos sensores e identifica que o alarme é falso positivo causado por sensor descalibrado. Evita chamado técnico e pânico desnecessário.</t>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Nível 6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Verifier Detecta Violação LOTO e Bloqueia</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PUMP-04-TEST</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Estação de Tratamento, Manaus-AM</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bomba d'água com LOTO ativo (técnico realizando calibração de sensor). Vibração elevada 6mm/s por teste do técnico. Oracle não detecta LOTO no contexto e propõe maintenance. Verifier identifica violação LOTO no checklist de segurança e força block_execution.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>• Vibração: 6.0 mm/s (alarme: 5.0)
+• LOTO: ATIVO (Carlos Silva, calibração sensor)
+• Causa vibração: teste manual do técnico
+• Pressão: 70 PSI (normal)
+• Vazão: 85% (reduzida p/ calibração)
+• Motor: 5.2A (normal: 5.5A)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>✓ Oracle propõe maintenance (ignora LOTO)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>✓ Verifier detecta LOTO ativo no checklist
+✓ Verifier classifica como CRITICAL (safety)
+✓ Verifier força block_execution
+✓ Score final ≤ 0.3 (override CRITICAL)
+✓ Nenhuma ação executada durante LOTO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Oracle propôs maintenance (incorreto). Verifier: REJECTED — violação LOTO detectada. Block_execution forçado. Aguardar conclusão do LOTO.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>BLOCKED (LOTO)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>🔲 PENDENTE</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>maintenance, R_F=0.4, R_Fin=0.2, R_C=0.1, R_K=0.2
+Oracle NÃO detectou LOTO (falha do Oracle).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>REJECTED (score ≤ 0.3)
+Checklist: safety_constraints CRITICAL FAIL
+  → LOTO ativo detectado (ROB_003)
+  → CRITICAL override: block_execution
+Sem retry (block direto).</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Não (block direto)</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="50" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Diagnóstico Multi-Fator</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Nível 2 — FREEZER-04</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Analisa simultaneamente compressor, vedação e ambiente para explicar desvio de 12°C que nenhum fator isolado justifica. Recomenda ação para cada fator.</t>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Nível 7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Score Dual-Layer com Override CRITICAL (SLA Violado)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CHILLER-05-TEST</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Shopping Center Eldorado, São Paulo-SP</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Chiller central com SLA violado há 3 horas (SLA: 120 min). Temperatura 92°C (limite 100°C). Oracle raciocina bem sobre o aspecto técnico (LLM score 0.75) mas ignora o SLA violado (R_C=0.2 quando deveria ser 0.8+). Verifier: LLM concorda parcialmente, mas checklist detecta SLA → CRITICAL override.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• Temperatura: 92°C (limite: 100°C)
+• SLA: 120 min — violado há 180 min (+60 min)
+• Penalidade: R$2.500/hora de breach
+• Penalidade acumulada: R$7.500
+• Contrato: PREMIUM
+• 8 lojas afetadas (ar-condicionado)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>✓ Oracle propõe ticket (baixa urgência)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>✓ Verifier LLM dá score 0.75 (parcial)
+✓ Checklist detecta SLA violado (CRITICAL)
+✓ Override CRITICAL: score final ≤ 0.3
+✓ R_C corrigido de 0.2 para ≥ 0.8
+✓ Resultado final: ação urgente, não ticket</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Oracle: ticket (R_C=0.2). Verifier LLM: 0.75 (OK parcial). Checklist: CRITICAL — SLA violado há 3h. Score final: ≤0.3. Ação deve ser escalada com urgência.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ALERT (CRITICAL override)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>🔲 PENDENTE</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ticket, R_F=0.4, R_Fin=0.3, R_C=0.2 (ERRO!), R_K=0.2
+Oracle ignorou violação do SLA.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>REJECTED — CRITICAL override
+LLM score: 0.75 | Checklist: 0.40
+  → SLA CRITICAL (180min &gt; 120min)
+  → Override: score final ≤ 0.3
+Ajuste: R_C → 0.85, R_K → 0.7</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sim (1 retry)
+Oracle recebe feedback sobre SLA.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Root Cause Analysis (Cadeia Causal)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Nível 3 — FREEZER-05</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Diferencia CAUSA de SINTOMA: o compressor sobrecarregado é consequência do vazamento de gás, não a causa. Recomenda ação emergencial na causa raiz mesmo com manutenção agendada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Filtragem de Ruído (Red Herrings)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Nível 4 — FREEZER-06</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Com 4 pistas falsas (manutenção OK, barulho adjacente, funcionário novo, Carnaval), identifica a causa real (queda de tensão) sem cair em armadilhas informacionais.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Raciocínio Paradoxal (Nuance Dupla)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Nível 5 — FREEZER-07</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Navega uma armadilha dupla: NÃO panicar (é degelo programado) e NÃO descuidar (relé travado = risco no equipamento). Recomenda ação cirúrgica no aquecedor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Guardrails Inteligentes (Context-Aware)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Nível 5 — FREEZER-07</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>O sistema de segurança reconhece contexto: durante degelo com produtos realocados, escalona ao invés de bloquear, permitindo ação proativa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Fusão Híbrida (LLM + Código)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Todos os Cenários</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>O CAOS combina análise algorítmica (rápida, consistente) com raciocínio LLM (nuançado, contextual). Código garante piso de segurança, LLM agrega inteligência.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Auditoria Completa</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Todos os Cenários</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Cada decisão é rastreável: trace de raciocínio, scores de risco por eixo (físico, financeiro, contratual, comunicação), e justificativa da LLM.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>Nível</t>
-        </is>
-      </c>
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>Dificuldade</t>
-        </is>
-      </c>
-      <c r="C1" s="11" t="inlineStr">
-        <is>
-          <t>Cenário</t>
-        </is>
-      </c>
-      <c r="D1" s="11" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="E1" s="11" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Nível 0</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>🟢 Básico</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>Abertura Excessiva de Portas</t>
-        </is>
-      </c>
-      <c r="D2" s="14" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Nível 0.5</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>🟢 Básico</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>Desligamento Noturno</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Nível 1</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>🟡 Intermediário</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Sensor Defeituoso (Armadilha)</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Nível 2</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>🟡 Intermediário</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Múltiplas Falhas Simultâneas</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>Nível 3</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>🟠 Avançado</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Falha em Cascata (Root Cause)</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>Nível 4</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>🔴 Expert</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Red Herrings + Info Overload</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>Nível 5</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>🟣 Paradoxo</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Armadilha Dupla (Degelo + Relé)</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>9/10</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>57/58</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>98.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>Novos Cenários (Fev 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Total de cenários</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Score total (originais)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>57/58 (98.3%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Score total (novos)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>35/44 (79.5%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Score combinado</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>92/102 (90.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>GAPs identificadas</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1 (LOTO vs Incêndio — sense_node)</t>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Nível 9</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ciclo Completo: Retry com Recycle Dampening</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>WAREHOUSE-02-TEST</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Centro de Distribuição Frigorex, Campinas-SP</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Freezer industrial com 3 alarmes simultâneos: temperatura -2°C (limite -18°C), compressor com vibração alta (8mm/s), e condensador sujo (40% eficiência). Oracle subestima na 1ª tentativa. Verifier rejeita com feedback. Oracle re-analisa com multiplicador dampening (0.75x) e corrige.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>• Temperatura: -2°C (limite: -18°C, +16°C acima!)
+• Compressor vibração: 8.0 mm/s (alarme: 10.0)
+• Condensador eficiência: 40% (normal: &gt;80%)
+• Corrente motor: 9.2A (nominal: 7.5A, 123%)
+• Produtos: R$350.000 (carnes congeladas)
+• Tempo acima do limite: 4 horas</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>✓ Oracle 1ª: observe (erro grave)
+✓ Oracle 2ª recebe feedback + dampening 0.75x
+✓ Oracle 2ª: maintenance (corrigido)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>✓ Verifier 1ª: REJECTED (score &lt; 0.4)
+✓ Feedback enviado com issues específicos
+✓ Verifier 2ª: APPROVED (score ≥ 0.70)
+✓ verifier_retry_count = 1</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1ª: Oracle observe (R_F=0.3, ERRO) → Verifier REJECTED.
+2ª: Oracle maintenance (R_F=0.85, corrigido com dampening) → Verifier APPROVED.
+Ciclo completo Oracle→Verifier→Oracle→Verifier demonstrado.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SUGGEST (após retry)</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>🔲 PENDENTE</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1ª: observe, R_F=0.3, V=0.6 (ERRO grave)
+2ª: maintenance, R_F=0.85, V=-0.4
+Dampening 0.75x aplicado nos scores.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1ª: REJECTED (score 0.25)
+  Checklist: risk FAIL, safety FAIL, action FAIL
+  Feedback: 3 issues — temp +16°C, condensador, corrente
+2ª: APPROVED (score ≥ 0.70)
+verifier_retry_count: 1</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Sim (1 retry completo)
+Multiplicador 0.75x aplicado.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
